--- a/Mass_update_AQUA/mass_update_AQUA_sts_fix.xlsx
+++ b/Mass_update_AQUA/mass_update_AQUA_sts_fix.xlsx
@@ -65,8 +65,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L192"/>
+  <dimension ref="A1:L185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a0R3g00000AB2ex</t>
+          <t>a0R6g00000DLKCI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -510,17 +510,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>46009</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>10330_AQU001_2</t>
@@ -528,7 +526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -540,17 +538,15 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L2" s="3" t="n">
-        <v>44755</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a0R3g00000AB2ey</t>
+          <t>a0RKf00000ExsRt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,47 +556,43 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10330_AQU001_2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>C#89525-32</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>46009</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10330_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>REU</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L3" s="3" t="n">
-        <v>44755</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a0R3g00000AB2ez</t>
+          <t>a0R3g00000AB2ex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -618,8 +610,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>46009</v>
+      <c r="E4" s="3" t="n">
+        <v>44755</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -640,17 +632,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="2" t="n">
         <v>44755</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a0R3g00000AB2f0</t>
+          <t>a0R3g00000AB2ey</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -668,8 +660,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>46009</v>
+      <c r="E5" s="3" t="n">
+        <v>44755</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -690,17 +682,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="2" t="n">
         <v>44755</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a0R6g00000DLKCI</t>
+          <t>a0R3g00000AB2ez</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -710,15 +702,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>44755</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>10330_AQU001_2</t>
@@ -726,7 +720,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>#AQUA</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -738,15 +732,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" s="2" t="n">
+        <v>44755</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a0RKf00000ExsRt</t>
+          <t>a0R3g00000AB2f0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,15 +752,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>44755</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>10330_AQU001_2</t>
@@ -772,27 +770,29 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C#89525-32</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>46009</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>REU</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" s="2" t="n">
+        <v>44755</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a0R3g0000093ELV</t>
+          <t>a0R6g00000DLKBt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -830,17 +830,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="2" t="n">
         <v>44777</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a0R6g00000HfHmQ</t>
+          <t>a0R3g0000093ELU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Not in Clinical Use</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554711</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -878,17 +878,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L9" s="3" t="n">
-        <v>45490</v>
+      <c r="L9" s="2" t="n">
+        <v>44777</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>a0R6g00000DLKBt</t>
+          <t>a0R3g0000093ELV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>#AQUA</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -926,17 +926,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="2" t="n">
         <v>44777</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>a0R3g0000093ELU</t>
+          <t>a0R6g00000HfHmQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Not in Clinical Use</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1554711</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -974,17 +974,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L11" s="3" t="n">
-        <v>44777</v>
+      <c r="L11" s="2" t="n">
+        <v>45490</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>a0R3g000000Tj3T</t>
+          <t>a0R3g000000U1rD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1022,17 +1022,17 @@
           <t>RNCA</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="2" t="n">
         <v>43851</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a0R3g000000U1rD</t>
+          <t>a0R3g000000Tj3T</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1042,15 +1042,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>43619</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>10632_AQU001_2</t>
@@ -1058,7 +1060,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>#AQUA</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1070,10 +1072,10 @@
           <t>RNCA</t>
         </is>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="2" t="n">
         <v>43851</v>
       </c>
     </row>
@@ -1118,10 +1120,10 @@
           <t>RNCA</t>
         </is>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="2" t="n">
         <v>43194</v>
       </c>
     </row>
@@ -1146,7 +1148,9 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" s="3" t="n">
+        <v>43619</v>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>10632_AQU001_2</t>
@@ -1166,10 +1170,10 @@
           <t>RNCA</t>
         </is>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="2" t="n">
         <v>43851</v>
       </c>
     </row>
@@ -1194,7 +1198,9 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" s="3" t="n">
+        <v>45054</v>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>10860_AQU001_2</t>
@@ -1214,17 +1220,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="2" t="n">
         <v>45054</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>a0R6g00000F0J1o</t>
+          <t>a0R6g00000F0J1r</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1250,7 +1256,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554715</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1262,17 +1268,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="2" t="n">
         <v>45054</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a0R6g00000F0J1p</t>
+          <t>a0R6g00000F0J1t</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1282,12 +1288,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1298,7 +1304,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1567024</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1310,17 +1316,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="2" t="n">
         <v>45054</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>a0R6g00000F0J1q</t>
+          <t>a0R6g00000F0J1o</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1330,12 +1336,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1358,17 +1364,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="2" t="n">
         <v>45054</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a0R6g00000F0J1r</t>
+          <t>a0R6g00000F0J1p</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1378,15 +1384,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>45054</v>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>10860_AQU001_2</t>
@@ -1394,7 +1402,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1554715</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1406,17 +1414,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="2" t="n">
         <v>45054</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a0R6g00000F0J1t</t>
+          <t>a0R6g00000F0J1q</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1426,15 +1434,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>45054</v>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>10860_AQU001_2</t>
@@ -1442,7 +1452,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1567024</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1454,10 +1464,10 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="2" t="n">
         <v>45054</v>
       </c>
     </row>
@@ -1493,7 +1503,7 @@
           <t>#AQUA</t>
         </is>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" s="2" t="n">
         <v>45029</v>
       </c>
       <c r="I22" t="n">
@@ -1504,17 +1514,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="2" t="n">
         <v>44552</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg6VE</t>
+          <t>a0RKf00000ExnON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1540,11 +1550,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>45596</v>
+          <t>C#89525-32</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>45982</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1554,17 +1564,15 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L23" s="3" t="n">
-        <v>45586</v>
-      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg6VF</t>
+          <t>a0R6g00000Hg6VE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1593,7 +1601,7 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="I24" t="n">
@@ -1604,17 +1612,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="2" t="n">
         <v>45586</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg6VG</t>
+          <t>a0R6g00000Hg6VF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1643,7 +1651,7 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="I25" t="n">
@@ -1654,17 +1662,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="2" t="n">
         <v>45586</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg6VH</t>
+          <t>a0R6g00000Hg6VG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1693,7 +1701,7 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="I26" t="n">
@@ -1704,17 +1712,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="2" t="n">
         <v>45586</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg6VI</t>
+          <t>a0R6g00000Hg6VH</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1743,7 +1751,7 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="I27" t="n">
@@ -1754,17 +1762,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="2" t="n">
         <v>45586</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg6VJ</t>
+          <t>a0R6g00000Hg6VI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1793,7 +1801,7 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="I28" t="n">
@@ -1804,17 +1812,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="2" t="n">
         <v>45586</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg6VK</t>
+          <t>a0R6g00000Hg6VJ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1843,7 +1851,7 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="I29" t="n">
@@ -1854,17 +1862,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="2" t="n">
         <v>45586</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg6VL</t>
+          <t>a0R6g00000Hg6VK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1893,7 +1901,7 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H30" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="I30" t="n">
@@ -1904,17 +1912,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="2" t="n">
         <v>45586</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg6VM</t>
+          <t>a0R6g00000Hg6VL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1924,17 +1932,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>45029</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>10886_AQU001_2</t>
@@ -1945,7 +1951,9 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" s="2" t="n">
+        <v>45596</v>
+      </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
@@ -1954,17 +1962,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="2" t="n">
         <v>45586</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg6VN</t>
+          <t>a0R6g00000Hg6VM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1982,7 +1990,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="3" t="n">
         <v>45029</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -2004,17 +2012,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="2" t="n">
         <v>45586</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>a0R3g000009Mnux</t>
+          <t>a0R6g00000Hg6VN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2024,15 +2032,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>45029</v>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>10886_AQU001_2</t>
@@ -2043,9 +2053,7 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H33" s="3" t="n">
-        <v>45029</v>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
         <v>1</v>
       </c>
@@ -2054,17 +2062,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L33" s="3" t="n">
-        <v>44615</v>
+      <c r="L33" s="2" t="n">
+        <v>45586</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>a0R3g00000966C6</t>
+          <t>a0R3g000009Mnux</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2090,10 +2098,10 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="n">
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
         <v>45029</v>
       </c>
       <c r="I34" t="n">
@@ -2104,17 +2112,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L34" s="3" t="n">
-        <v>44552</v>
+      <c r="L34" s="2" t="n">
+        <v>44615</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>a0RKf00000ExnON</t>
+          <t>a0R3g00000966C6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2140,11 +2148,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C#89525-32</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>45982</v>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>45029</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -2154,10 +2162,12 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" s="2" t="n">
+        <v>44552</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2191,7 +2201,7 @@
           <t>#AQUA</t>
         </is>
       </c>
-      <c r="H36" s="3" t="n">
+      <c r="H36" s="2" t="n">
         <v>44762</v>
       </c>
       <c r="I36" t="n">
@@ -2202,17 +2212,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="2" t="n">
         <v>44656</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>a0R6g00000H2ta3</t>
+          <t>a0R3g000009bskG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2238,11 +2248,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>46182</v>
+          <t>1554715</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>44762</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -2252,17 +2262,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L37" s="3" t="n">
-        <v>45392</v>
+      <c r="L37" s="2" t="n">
+        <v>44656</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>a0R3g000009bskC</t>
+          <t>a0R3g000009bskF</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2272,28 +2282,28 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11320_AQU001_2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1554713</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
         <v>44762</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>11320_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>1</v>
       </c>
@@ -2302,17 +2312,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="2" t="n">
         <v>44656</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>a0R3g000009bskD</t>
+          <t>a0R6g00000HgTKE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2322,17 +2332,15 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>44762</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>11320_AQU001_2</t>
@@ -2340,10 +2348,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>1567895</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>45639</v>
+      </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
@@ -2352,17 +2362,15 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>44656</v>
-      </c>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>a0R3g000009bskE</t>
+          <t>a0R6g00000H2ta3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2372,17 +2380,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>44762</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>11320_AQU001_2</t>
@@ -2393,7 +2399,9 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" s="2" t="n">
+        <v>46182</v>
+      </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
@@ -2402,17 +2410,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L40" s="3" t="n">
-        <v>44656</v>
+      <c r="L40" s="2" t="n">
+        <v>45392</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>a0R3g000009bskF</t>
+          <t>a0R3g000009bskC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2422,15 +2430,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>44656</v>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>11320_AQU001_2</t>
@@ -2438,12 +2448,10 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1554713</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>44762</v>
-      </c>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
         <v>1</v>
       </c>
@@ -2452,17 +2460,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="2" t="n">
         <v>44656</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>a0R3g000009bskG</t>
+          <t>a0R3g000009bskD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2472,15 +2480,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>44656</v>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>11320_AQU001_2</t>
@@ -2488,12 +2498,10 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1554715</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>44762</v>
-      </c>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>1</v>
       </c>
@@ -2502,17 +2510,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="2" t="n">
         <v>44656</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>a0R6g00000HgTKE</t>
+          <t>a0R3g000009bskE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2522,15 +2530,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>44656</v>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>11320_AQU001_2</t>
@@ -2538,12 +2548,10 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>45639</v>
-      </c>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>1</v>
       </c>
@@ -2552,10 +2560,12 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" s="2" t="n">
+        <v>44656</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2578,8 +2588,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>45411</v>
+      <c r="E44" s="3" t="n">
+        <v>44963</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2600,10 +2610,10 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="2" t="n">
         <v>44963</v>
       </c>
     </row>
@@ -2628,8 +2638,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>45411</v>
+      <c r="E45" s="3" t="n">
+        <v>44963</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2650,17 +2660,17 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="2" t="n">
         <v>44963</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>a0R6g00000H2A6f</t>
+          <t>a0R6g00000HyTMQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2686,10 +2696,10 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="n">
+          <t>1554711</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="I46" t="n">
@@ -2700,17 +2710,17 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="2" t="n">
         <v>45334</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>a0R6g00000H2A6g</t>
+          <t>a0R6g00000H2A6f</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2739,7 +2749,7 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="H47" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="I47" t="n">
@@ -2750,17 +2760,17 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L47" s="3" t="n">
+      <c r="L47" s="2" t="n">
         <v>45334</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>a0R6g00000H2A6h</t>
+          <t>a0R6g00000H2A6g</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2789,7 +2799,7 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H48" s="3" t="n">
+      <c r="H48" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="I48" t="n">
@@ -2800,17 +2810,17 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="K48" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L48" s="3" t="n">
+      <c r="L48" s="2" t="n">
         <v>45334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>a0R6g00000HyTMQ</t>
+          <t>a0R6g00000H2A6h</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2836,10 +2846,10 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1554711</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="n">
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="I49" t="n">
@@ -2850,10 +2860,10 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="K49" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L49" s="3" t="n">
+      <c r="L49" s="2" t="n">
         <v>45334</v>
       </c>
     </row>
@@ -2878,8 +2888,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>46115</v>
+      <c r="E50" s="3" t="n">
+        <v>45880</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2900,10 +2910,10 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K50" s="3" t="n">
+      <c r="K50" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L50" s="3" t="n">
+      <c r="L50" s="2" t="n">
         <v>45880</v>
       </c>
     </row>
@@ -2939,7 +2949,7 @@
           <t>C#89528</t>
         </is>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="H51" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="I51" t="n">
@@ -2950,10 +2960,10 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="K51" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L51" s="3" t="n">
+      <c r="L51" s="2" t="n">
         <v>45880</v>
       </c>
     </row>
@@ -2989,7 +2999,7 @@
           <t>C#89527</t>
         </is>
       </c>
-      <c r="H52" s="3" t="n">
+      <c r="H52" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="I52" t="n">
@@ -3000,10 +3010,10 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K52" s="3" t="n">
+      <c r="K52" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L52" s="3" t="n">
+      <c r="L52" s="2" t="n">
         <v>45880</v>
       </c>
     </row>
@@ -3039,7 +3049,7 @@
           <t>C#89525-32</t>
         </is>
       </c>
-      <c r="H53" s="3" t="n">
+      <c r="H53" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="I53" t="n">
@@ -3050,10 +3060,10 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K53" s="3" t="n">
+      <c r="K53" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L53" s="3" t="n">
+      <c r="L53" s="2" t="n">
         <v>45880</v>
       </c>
     </row>
@@ -3098,7 +3108,7 @@
           <t>RNCA</t>
         </is>
       </c>
-      <c r="K54" s="3" t="n">
+      <c r="K54" s="2" t="n">
         <v>38011</v>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3124,8 +3134,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n">
-        <v>43812</v>
+      <c r="E55" s="3" t="n">
+        <v>42762</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3146,17 +3156,17 @@
           <t>RNCA</t>
         </is>
       </c>
-      <c r="K55" s="3" t="n">
+      <c r="K55" s="2" t="n">
         <v>38011</v>
       </c>
-      <c r="L55" s="3" t="n">
+      <c r="L55" s="2" t="n">
         <v>42762</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>a0R3g000000Te3F</t>
+          <t>a0R3g000000Te3K</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3182,10 +3192,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>1541637</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>43812</v>
+      </c>
       <c r="I56" t="n">
         <v>1</v>
       </c>
@@ -3194,7 +3206,7 @@
           <t>RNCA</t>
         </is>
       </c>
-      <c r="K56" s="3" t="n">
+      <c r="K56" s="2" t="n">
         <v>38011</v>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3202,7 +3214,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>a0R3g000000Te3K</t>
+          <t>a0R3g000000Te3F</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3228,12 +3240,10 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1541637</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>43812</v>
-      </c>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>1</v>
       </c>
@@ -3242,7 +3252,7 @@
           <t>RNCA</t>
         </is>
       </c>
-      <c r="K57" s="3" t="n">
+      <c r="K57" s="2" t="n">
         <v>38011</v>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3250,7 +3260,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>a0R6g00000DLK9E</t>
+          <t>a0R0d000006Sq5N</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3271,7 +3281,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>12548_AQU001_2</t>
+          <t>12619_AQU001_2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3288,17 +3298,15 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K58" s="3" t="n">
+      <c r="K58" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L58" s="3" t="n">
-        <v>44116</v>
-      </c>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>a0R3g000000UTUc</t>
+          <t>a0R0d000006IYbs</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3319,15 +3327,17 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>12548_AQU001_2</t>
+          <t>12619_AQU001_2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>1517663</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>43503</v>
+      </c>
       <c r="I59" t="n">
         <v>1</v>
       </c>
@@ -3336,17 +3346,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K59" s="3" t="n">
+      <c r="K59" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L59" s="3" t="n">
-        <v>44116</v>
+      <c r="L59" s="2" t="n">
+        <v>43264</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>a0R3g000000UTUd</t>
+          <t>a0R0d000006IYbt</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3356,23 +3366,25 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>43264</v>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>12548_AQU001_2</t>
+          <t>12619_AQU001_2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1517663</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3384,17 +3396,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K60" s="3" t="n">
+      <c r="K60" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L60" s="3" t="n">
-        <v>44116</v>
+      <c r="L60" s="2" t="n">
+        <v>43264</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>a0R3g000000UTUe</t>
+          <t>a0R0d000006IYbu</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3404,23 +3416,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>43264</v>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>12548_AQU001_2</t>
+          <t>12619_AQU001_2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1517663</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3432,17 +3446,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K61" s="3" t="n">
+      <c r="K61" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L61" s="3" t="n">
-        <v>44116</v>
+      <c r="L61" s="2" t="n">
+        <v>43264</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>a0R3g000000UTUf</t>
+          <t>a0R6g00000H3Jb6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3463,15 +3477,17 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>12548_AQU001_2</t>
+          <t>12619_AQU001_2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>1567895</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>45184</v>
+      </c>
       <c r="I62" t="n">
         <v>1</v>
       </c>
@@ -3480,17 +3496,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K62" s="3" t="n">
+      <c r="K62" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L62" s="3" t="n">
-        <v>44116</v>
+      <c r="L62" s="2" t="n">
+        <v>43264</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>a0R3g000000UTUg</t>
+          <t>a0R6g00000H0M6i</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3511,15 +3527,17 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>12548_AQU001_2</t>
+          <t>12736_AQU001_2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>#AQUA</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>45327</v>
+      </c>
       <c r="I63" t="n">
         <v>1</v>
       </c>
@@ -3528,17 +3546,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K63" s="3" t="n">
+      <c r="K63" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L63" s="3" t="n">
-        <v>44116</v>
+      <c r="L63" s="2" t="n">
+        <v>45246</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>a0R3g000000UTUb</t>
+          <t>a0R6g00000H0KEZ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3548,26 +3566,28 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Not in Clinical Use</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>12548_AQU001_2</t>
+          <t>12736_AQU001_2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1541637</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>1554713</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>45327</v>
+      </c>
       <c r="I64" t="n">
         <v>1</v>
       </c>
@@ -3576,17 +3596,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K64" s="3" t="n">
+      <c r="K64" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L64" s="3" t="n">
-        <v>44116</v>
+      <c r="L64" s="2" t="n">
+        <v>45246</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>a0R0d000006IYbs</t>
+          <t>a0RQQ00000HpSN3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3607,16 +3627,16 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>12619_AQU001_2</t>
+          <t>12736_AQU001_2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1517663</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>43503</v>
+          <t>C#89525-32</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>46070</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -3626,17 +3646,15 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K65" s="3" t="n">
+      <c r="K65" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L65" s="3" t="n">
-        <v>43264</v>
-      </c>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>a0R0d000006IYbt</t>
+          <t>a0R6g00000H0KEX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3646,28 +3664,28 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="n">
-        <v>43503</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>12619_AQU001_2</t>
+          <t>12736_AQU001_2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1517663</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>45327</v>
+      </c>
       <c r="I66" t="n">
         <v>1</v>
       </c>
@@ -3676,17 +3694,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K66" s="3" t="n">
+      <c r="K66" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L66" s="3" t="n">
-        <v>43264</v>
+      <c r="L66" s="2" t="n">
+        <v>45246</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>a0R0d000006IYbu</t>
+          <t>a0R6g00000H0KEY</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3696,28 +3714,28 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>43503</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>12619_AQU001_2</t>
+          <t>12736_AQU001_2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1517663</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>45327</v>
+      </c>
       <c r="I67" t="n">
         <v>1</v>
       </c>
@@ -3726,17 +3744,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K67" s="3" t="n">
+      <c r="K67" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L67" s="3" t="n">
-        <v>43264</v>
+      <c r="L67" s="2" t="n">
+        <v>45246</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>a0R0d000006Sq5N</t>
+          <t>a0RKf00000KffTr</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3746,23 +3764,25 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>45327</v>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>12619_AQU001_2</t>
+          <t>12736_AQU001_2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>#AQUA</t>
+          <t>C#89526</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -3774,15 +3794,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K68" s="3" t="n">
+      <c r="K68" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" s="2" t="n">
+        <v>45975</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>a0R6g00000H3Jb6</t>
+          <t>a0R3g000009Rxei</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3803,17 +3825,15 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>12619_AQU001_2</t>
+          <t>12894_AQU001_2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>45184</v>
-      </c>
+          <t>#AQUA</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
         <v>1</v>
       </c>
@@ -3822,17 +3842,15 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K69" s="3" t="n">
+      <c r="K69" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L69" s="3" t="n">
-        <v>43264</v>
-      </c>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>a0R6g00000H0M6i</t>
+          <t>a0R3g000006jths</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3853,17 +3871,15 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>12736_AQU001_2</t>
+          <t>12894_AQU001_2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="n">
-        <v>45327</v>
-      </c>
+          <t>1543771</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
         <v>1</v>
       </c>
@@ -3872,17 +3888,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K70" s="3" t="n">
+      <c r="K70" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L70" s="3" t="n">
-        <v>45246</v>
+      <c r="L70" s="2" t="n">
+        <v>44292</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>a0R6g00000H0KEX</t>
+          <t>a0R3g000006jtht</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3892,28 +3908,28 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>44292</v>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>12736_AQU001_2</t>
+          <t>12894_AQU001_2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>45327</v>
-      </c>
+          <t>1543771</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
         <v>1</v>
       </c>
@@ -3922,17 +3938,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K71" s="3" t="n">
+      <c r="K71" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L71" s="3" t="n">
-        <v>45246</v>
+      <c r="L71" s="2" t="n">
+        <v>44292</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>a0R6g00000H0KEY</t>
+          <t>a0R6g00000Hg5Ub</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3953,16 +3969,16 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>12736_AQU001_2</t>
+          <t>12894_AQU001_2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>45327</v>
+          <t>1567895</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>45579</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -3972,17 +3988,15 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K72" s="3" t="n">
+      <c r="K72" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L72" s="3" t="n">
-        <v>45246</v>
-      </c>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>a0R6g00000H0KEZ</t>
+          <t>a0R3g000006jthw</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4003,17 +4017,15 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>12736_AQU001_2</t>
+          <t>12894_AQU001_2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1554713</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>45327</v>
-      </c>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
         <v>1</v>
       </c>
@@ -4022,17 +4034,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K73" s="3" t="n">
+      <c r="K73" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L73" s="3" t="n">
-        <v>45246</v>
+      <c r="L73" s="2" t="n">
+        <v>44292</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>a0RKf00000KffTr</t>
+          <t>a0R3g000006jthx</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4050,17 +4062,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E74" s="2" t="n">
-        <v>45327</v>
+      <c r="E74" s="3" t="n">
+        <v>44292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>12736_AQU001_2</t>
+          <t>12894_AQU001_2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C#89526</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -4072,17 +4084,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K74" s="3" t="n">
+      <c r="K74" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L74" s="3" t="n">
-        <v>45975</v>
+      <c r="L74" s="2" t="n">
+        <v>44292</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>a0RQQ00000HpSN3</t>
+          <t>a0R3g000006jthy</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4092,28 +4104,28 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>44292</v>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>12736_AQU001_2</t>
+          <t>12894_AQU001_2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C#89525-32</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>46070</v>
-      </c>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
         <v>1</v>
       </c>
@@ -4122,15 +4134,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K75" s="3" t="n">
+      <c r="K75" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="L75" s="2" t="n">
+        <v>44292</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>a0R3g000009Rxei</t>
+          <t>a0R6g00000DLK7J</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4151,7 +4165,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>12894_AQU001_2</t>
+          <t>13120_AQU001_2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4159,24 +4173,28 @@
           <t>#AQUA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" s="2" t="n">
+        <v>45222</v>
+      </c>
       <c r="I76" t="n">
         <v>1</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L76" t="inlineStr"/>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>37010</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>44760</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>a0R3g000006jths</t>
+          <t>a0R3g00000ACF5v</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4197,34 +4215,36 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>12894_AQU001_2</t>
+          <t>13120_AQU001_2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1543771</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>1554714</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>45222</v>
+      </c>
       <c r="I77" t="n">
         <v>1</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>44292</v>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>37010</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>44760</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>a0R3g000006jtht</t>
+          <t>a0RKf00000ExtxL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4234,47 +4254,43 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>45579</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>12894_AQU001_2</t>
+          <t>13120_AQU001_2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1543771</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="n">
-        <v>1</v>
-      </c>
+          <t>C#89525-32</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>44292</v>
-      </c>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>37010</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>a0R3g000006jthw</t>
+          <t>a0R6g00000HfD8T</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4284,23 +4300,25 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>45222</v>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>12894_AQU001_2</t>
+          <t>13120_AQU001_2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -4309,20 +4327,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>44292</v>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>37010</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>45477</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>a0R3g000006jthx</t>
+          <t>a0R32000004qcN8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4332,25 +4350,23 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>45579</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>12894_AQU001_2</t>
+          <t>13219_AQU001_2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -4359,20 +4375,18 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>44292</v>
-      </c>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>38664</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>a0R3g000006jthy</t>
+          <t>a0R3g00000AA9Uq</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4382,47 +4396,45 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>45579</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>12894_AQU001_2</t>
+          <t>13219_AQU001_2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>1554711</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>44740</v>
+      </c>
       <c r="I81" t="n">
         <v>1</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>44292</v>
-      </c>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>38664</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg5Ub</t>
+          <t>a0R6g00000EW4aL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4443,34 +4455,36 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>12894_AQU001_2</t>
+          <t>13219_AQU001_2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="n">
-        <v>45579</v>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>45356</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K82" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L82" t="inlineStr"/>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>38664</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>45204</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>a0R6g00000HfD8T</t>
+          <t>a0R6g00000H0iRM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4488,12 +4502,12 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E83" s="2" t="n">
-        <v>45222</v>
+      <c r="E83" s="3" t="n">
+        <v>42809</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>13120_AQU001_2</t>
+          <t>13219_AQU001_2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4510,17 +4524,17 @@
           <t>RNCA</t>
         </is>
       </c>
-      <c r="K83" s="3" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>45477</v>
+      <c r="K83" s="2" t="n">
+        <v>38664</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>45301</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>a0R3g00000ACF5v</t>
+          <t>a0R6g00000F0cZ3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4541,36 +4555,36 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>13120_AQU001_2</t>
+          <t>13496_AQU001_2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1554714</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>45222</v>
+          <t>#AQUA</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>45229</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>44760</v>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>41487</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>45086</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>a0R6g00000DLK7J</t>
+          <t>a0R6g00000H2mbP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4580,47 +4594,47 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>45229</v>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>13120_AQU001_2</t>
+          <t>13496_AQU001_2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>45222</v>
-      </c>
+          <t>1554715</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
         <v>1</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>44760</v>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>41487</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>45376</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>a0RKf00000ExtxL</t>
+          <t>a0R6g00000F0bmh</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4641,32 +4655,36 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>13120_AQU001_2</t>
+          <t>13496_AQU001_2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>C#89525-32</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>46021</v>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>1554711</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>45229</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L86" t="inlineStr"/>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>41487</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>45086</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>a0R32000004qcN8</t>
+          <t>a0R6g00000F0bmi</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4687,32 +4705,36 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>13219_AQU001_2</t>
+          <t>13496_AQU001_2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>45229</v>
+      </c>
       <c r="I87" t="n">
         <v>1</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>38664</v>
-      </c>
-      <c r="L87" t="inlineStr"/>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>41487</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>45086</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>a0R6g00000EW4aL</t>
+          <t>a0R6g00000H2mbO</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4722,18 +4744,20 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>45229</v>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>13219_AQU001_2</t>
+          <t>13496_AQU001_2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4741,28 +4765,26 @@
           <t>1554712</t>
         </is>
       </c>
-      <c r="H88" s="3" t="n">
-        <v>45356</v>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
         <v>1</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>38664</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>45204</v>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>41487</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>45376</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>a0R6g00000H0iRM</t>
+          <t>a0R6g00000HgI3Z</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4780,17 +4802,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E89" s="2" t="n">
-        <v>44740</v>
+      <c r="E89" s="3" t="n">
+        <v>45614</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>13219_AQU001_2</t>
+          <t>16578_AQU001_2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -4799,20 +4821,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>38664</v>
-      </c>
-      <c r="L89" s="3" t="n">
-        <v>45301</v>
+          <t>RJP</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>37379</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>45614</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>a0R3g00000AA9Uq</t>
+          <t>a0R6g00000HgHty</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4833,34 +4855,36 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>13219_AQU001_2</t>
+          <t>16578_AQU001_2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1554711</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>44740</v>
+          <t>C#89528</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>45769</v>
       </c>
       <c r="I90" t="n">
         <v>1</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>38664</v>
-      </c>
-      <c r="L90" t="inlineStr"/>
+          <t>RJP</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>37379</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>45614</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>a0R6g00000F0cZ3</t>
+          <t>a0R6g00000HgHtw</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4881,36 +4905,36 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>13496_AQU001_2</t>
+          <t>16578_AQU001_2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>45229</v>
+          <t>1567895</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>45769</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>41487</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>45086</v>
+          <t>RJP</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>37379</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>45614</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>a0R6g00000H2mbP</t>
+          <t>a0R6g00000HgHtx</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4920,47 +4944,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>45229</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>13496_AQU001_2</t>
+          <t>16578_AQU001_2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1554715</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>C#89526</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>45769</v>
+      </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="n">
-        <v>41487</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>45376</v>
+          <t>RJP</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>37379</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>45614</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>a0R6g00000F0bmi</t>
+          <t>a0R0d000006TGFn</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4981,36 +5005,32 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>13496_AQU001_2</t>
+          <t>16635_AQU001_2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>45229</v>
-      </c>
+          <t>#AQUA</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
         <v>1</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="n">
-        <v>41487</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>45086</v>
-      </c>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>a0R6g00000H2mbO</t>
+          <t>a0R0d000006ZwAQ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5020,47 +5040,47 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>45229</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>13496_AQU001_2</t>
+          <t>16635_AQU001_2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>1517663</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>43648</v>
+      </c>
       <c r="I94" t="n">
         <v>1</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="n">
-        <v>41487</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>45376</v>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>43434</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>a0R6g00000F0bmh</t>
+          <t>a0R0d000006ZwAN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5081,36 +5101,36 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>13496_AQU001_2</t>
+          <t>16635_AQU001_2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1554711</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>45229</v>
+          <t>1517663</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>43648</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K95" s="3" t="n">
-        <v>41487</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>45086</v>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>43434</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>a0R6g00000HgI3Z</t>
+          <t>a0R0d000006ZwAO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5120,47 +5140,47 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>45769</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>16578_AQU001_2</t>
+          <t>16635_AQU001_2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>1517663</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>43648</v>
+      </c>
       <c r="I96" t="n">
         <v>1</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>RJP</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="n">
-        <v>37379</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>45614</v>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>43434</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>a0R6g00000HgHtx</t>
+          <t>a0R0d000006ZwAP</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5181,36 +5201,36 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>16578_AQU001_2</t>
+          <t>16635_AQU001_2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C#89526</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>45769</v>
+          <t>1517663</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>43648</v>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>RJP</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="n">
-        <v>37379</v>
-      </c>
-      <c r="L97" s="3" t="n">
-        <v>45614</v>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>43434</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>a0R6g00000HgHty</t>
+          <t>a0R3g000000Ta0N</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5220,47 +5240,47 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>43648</v>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>16578_AQU001_2</t>
+          <t>16635_AQU001_2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>C#89528</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="n">
-        <v>45769</v>
-      </c>
+          <t>1543771</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
         <v>1</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>RJP</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="n">
-        <v>37379</v>
-      </c>
-      <c r="L98" s="3" t="n">
-        <v>45614</v>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>43789</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>a0R6g00000HgHtw</t>
+          <t>a0R3g000000Ta0O</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5270,47 +5290,47 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>43648</v>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>16578_AQU001_2</t>
+          <t>16635_AQU001_2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="n">
-        <v>45769</v>
-      </c>
+          <t>1543771</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
         <v>1</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>RJP</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="n">
-        <v>37379</v>
-      </c>
-      <c r="L99" s="3" t="n">
-        <v>45614</v>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>43789</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>a0R0d000006TGFn</t>
+          <t>a0R3g000000Ta0P</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5320,15 +5340,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>43648</v>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>16635_AQU001_2</t>
@@ -5336,7 +5358,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>#AQUA</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -5348,15 +5370,17 @@
           <t>RCH</t>
         </is>
       </c>
-      <c r="K100" s="3" t="n">
+      <c r="K100" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="L100" t="inlineStr"/>
+      <c r="L100" s="2" t="n">
+        <v>43789</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0Q</t>
+          <t>a0R6g00000H3DPp</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5366,17 +5390,15 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>43648</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>16635_AQU001_2</t>
@@ -5384,10 +5406,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>1567895</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>45440</v>
+      </c>
       <c r="I101" t="n">
         <v>1</v>
       </c>
@@ -5396,17 +5420,15 @@
           <t>RCH</t>
         </is>
       </c>
-      <c r="K101" s="3" t="n">
+      <c r="K101" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="L101" s="3" t="n">
-        <v>43789</v>
-      </c>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0R</t>
+          <t>a0R3g000000Ta0Q</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5424,7 +5446,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E102" s="2" t="n">
+      <c r="E102" s="3" t="n">
         <v>43648</v>
       </c>
       <c r="F102" t="inlineStr">
@@ -5446,17 +5468,17 @@
           <t>RCH</t>
         </is>
       </c>
-      <c r="K102" s="3" t="n">
+      <c r="K102" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="L102" s="3" t="n">
+      <c r="L102" s="2" t="n">
         <v>43789</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0S</t>
+          <t>a0R3g000000Ta0R</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5474,7 +5496,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="E103" s="3" t="n">
         <v>43648</v>
       </c>
       <c r="F103" t="inlineStr">
@@ -5496,17 +5518,17 @@
           <t>RCH</t>
         </is>
       </c>
-      <c r="K103" s="3" t="n">
+      <c r="K103" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="L103" s="3" t="n">
+      <c r="L103" s="2" t="n">
         <v>43789</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>a0R0d000006ZwAN</t>
+          <t>a0R3g000000Ta0S</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5516,15 +5538,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>43648</v>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>16635_AQU001_2</t>
@@ -5532,12 +5556,10 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1517663</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="n">
-        <v>43648</v>
-      </c>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
         <v>1</v>
       </c>
@@ -5546,17 +5568,17 @@
           <t>RCH</t>
         </is>
       </c>
-      <c r="K104" s="3" t="n">
+      <c r="K104" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="L104" s="3" t="n">
-        <v>43434</v>
+      <c r="L104" s="2" t="n">
+        <v>43789</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>a0R0d000006ZwAO</t>
+          <t>a0R3g000008eyS7</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5577,36 +5599,32 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>16635_AQU001_2</t>
+          <t>16827_AQU001_2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1517663</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="n">
-        <v>43648</v>
-      </c>
+          <t>#AQUA</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
         <v>1</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L105" s="3" t="n">
-        <v>43434</v>
-      </c>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>a0R0d000006ZwAP</t>
+          <t>a0R3g0000088TZi</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5616,47 +5634,47 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>44250</v>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>16635_AQU001_2</t>
+          <t>16827_AQU001_2</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1517663</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>43648</v>
-      </c>
+          <t>1543770</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
         <v>1</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L106" s="3" t="n">
-        <v>43434</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>44368</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>a0R0d000006ZwAQ</t>
+          <t>a0R6g00000H0QPy</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5677,36 +5695,32 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>16635_AQU001_2</t>
+          <t>16827_AQU001_2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1517663</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>43648</v>
-      </c>
+          <t>1554711</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
         <v>1</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L107" s="3" t="n">
-        <v>43434</v>
-      </c>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0N</t>
+          <t>a0R3g0000067v5X</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5716,47 +5730,47 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>43648</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>16635_AQU001_2</t>
+          <t>16827_AQU001_2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1543771</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>44250</v>
+      </c>
       <c r="I108" t="n">
         <v>1</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K108" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L108" s="3" t="n">
-        <v>43789</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>44159</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0O</t>
+          <t>a0R3g000000Tx2x</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5766,47 +5780,47 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>43648</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>16635_AQU001_2</t>
+          <t>16827_AQU001_2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1543771</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>44530</v>
+      </c>
       <c r="I109" t="n">
         <v>1</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K109" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L109" s="3" t="n">
-        <v>43789</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>43925</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0P</t>
+          <t>a0R3g000009Cn8h</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5824,17 +5838,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E110" s="2" t="n">
-        <v>43648</v>
+      <c r="E110" s="3" t="n">
+        <v>44250</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>16635_AQU001_2</t>
+          <t>16827_AQU001_2</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -5843,20 +5857,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K110" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L110" s="3" t="n">
-        <v>43789</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>44574</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>a0R6g00000H3DPp</t>
+          <t>a0R6g00000H0I1a</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5866,45 +5880,47 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>44250</v>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>16635_AQU001_2</t>
+          <t>16827_AQU001_2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H111" s="3" t="n">
-        <v>45440</v>
-      </c>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
         <v>1</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K111" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L111" t="inlineStr"/>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>45240</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>a0R3g000008eyS7</t>
+          <t>a0R3g000009Rx1B</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5925,7 +5941,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>16827_AQU001_2</t>
+          <t>17158_AQU001_2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -5942,7 +5958,7 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K112" s="3" t="n">
+      <c r="K112" s="2" t="n">
         <v>41089</v>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -5950,7 +5966,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>a0R3g0000088TZi</t>
+          <t>a0R3g000000an4j</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5960,28 +5976,28 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>44250</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>16827_AQU001_2</t>
+          <t>17158_AQU001_2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1543770</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>1543771</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>44642</v>
+      </c>
       <c r="I113" t="n">
         <v>1</v>
       </c>
@@ -5990,17 +6006,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K113" s="3" t="n">
+      <c r="K113" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L113" s="3" t="n">
-        <v>44368</v>
+      <c r="L113" s="2" t="n">
+        <v>44266</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>a0R3g0000067v5X</t>
+          <t>a0R6g00000DLK4n</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6021,16 +6037,16 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>16827_AQU001_2</t>
+          <t>17158_AQU001_2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="n">
-        <v>44250</v>
+          <t>1554711</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>44642</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
@@ -6040,17 +6056,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K114" s="3" t="n">
+      <c r="K114" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L114" s="3" t="n">
-        <v>44159</v>
+      <c r="L114" s="2" t="n">
+        <v>44266</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>a0R3g000000Tx2x</t>
+          <t>a0R3g000000an4k</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6071,7 +6087,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>16827_AQU001_2</t>
+          <t>17158_AQU001_2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6079,8 +6095,8 @@
           <t>1541636</t>
         </is>
       </c>
-      <c r="H115" s="3" t="n">
-        <v>44530</v>
+      <c r="H115" s="2" t="n">
+        <v>44642</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
@@ -6090,17 +6106,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K115" s="3" t="n">
+      <c r="K115" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L115" s="3" t="n">
-        <v>43925</v>
+      <c r="L115" s="2" t="n">
+        <v>44266</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>a0R3g000009Cn8h</t>
+          <t>a0R3g000000an4l</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6118,17 +6134,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E116" s="2" t="n">
-        <v>44250</v>
+      <c r="E116" s="3" t="n">
+        <v>44266</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>16827_AQU001_2</t>
+          <t>17158_AQU001_2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -6140,17 +6156,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K116" s="3" t="n">
+      <c r="K116" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L116" s="3" t="n">
-        <v>44574</v>
+      <c r="L116" s="2" t="n">
+        <v>44266</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>a0R6g00000H0I1a</t>
+          <t>a0R6g00000HgXw3</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6168,17 +6184,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E117" s="2" t="n">
-        <v>44250</v>
+      <c r="E117" s="3" t="n">
+        <v>45636</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>16827_AQU001_2</t>
+          <t>17368_AQU001_2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -6187,20 +6203,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L117" s="3" t="n">
-        <v>45240</v>
+          <t>RJP</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>39036</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>45636</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>a0R6g00000H0QPy</t>
+          <t>a0R6g00000HgPZb</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6221,32 +6237,36 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>16827_AQU001_2</t>
+          <t>17368_AQU001_2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1554711</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>1567895</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>45734</v>
+      </c>
       <c r="I118" t="n">
         <v>1</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L118" t="inlineStr"/>
+          <t>RJP</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>39036</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>45636</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>a0R3g000009Rx1B</t>
+          <t>a0R6g00000HgPZc</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6267,32 +6287,36 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>17158_AQU001_2</t>
+          <t>17368_AQU001_2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>C#89526</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>45734</v>
+      </c>
       <c r="I119" t="n">
         <v>1</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K119" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L119" t="inlineStr"/>
+          <t>RJP</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>39036</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>45636</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>a0R3g000000an4k</t>
+          <t>a0R6g00000EUugN</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6313,17 +6337,15 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>17158_AQU001_2</t>
+          <t>18779_AQU001_2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="n">
-        <v>44642</v>
-      </c>
+          <t>#AQUA</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
         <v>1</v>
       </c>
@@ -6332,17 +6354,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K120" s="3" t="n">
+      <c r="K120" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L120" s="3" t="n">
-        <v>44266</v>
+      <c r="L120" s="2" t="n">
+        <v>45030</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>a0R3g000000an4l</t>
+          <t>a0RKf00000JM5pl</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6352,28 +6374,28 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>44642</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>17158_AQU001_2</t>
+          <t>18779_AQU001_2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>1567895</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>45756</v>
+      </c>
       <c r="I121" t="n">
         <v>1</v>
       </c>
@@ -6382,17 +6404,15 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K121" s="3" t="n">
+      <c r="K121" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L121" s="3" t="n">
-        <v>44266</v>
-      </c>
+      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>a0R3g000000an4j</t>
+          <t>a0RQQ00000HzOOb</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6402,28 +6422,28 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>45177</v>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>17158_AQU001_2</t>
+          <t>18779_AQU001_2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1543771</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="n">
-        <v>44642</v>
-      </c>
+          <t>C#89526</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
         <v>1</v>
       </c>
@@ -6432,17 +6452,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K122" s="3" t="n">
+      <c r="K122" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L122" s="3" t="n">
-        <v>44266</v>
+      <c r="L122" s="2" t="n">
+        <v>46076</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>a0R6g00000DLK4n</t>
+          <t>a0R6g00000EUtiY</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6463,17 +6483,15 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>17158_AQU001_2</t>
+          <t>18779_AQU001_2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1554711</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="n">
-        <v>44642</v>
-      </c>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
         <v>1</v>
       </c>
@@ -6482,17 +6500,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K123" s="3" t="n">
+      <c r="K123" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L123" s="3" t="n">
-        <v>44266</v>
+      <c r="L123" s="2" t="n">
+        <v>45030</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>a0R6g00000HgXw3</t>
+          <t>a0R6g00000DLK3u</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6502,20 +6520,18 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>45734</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>17368_AQU001_2</t>
+          <t>19096_AQU001_2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -6523,26 +6539,28 @@
           <t>#AQUA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" s="2" t="n">
+        <v>45088</v>
+      </c>
       <c r="I124" t="n">
         <v>1</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>RJP</t>
-        </is>
-      </c>
-      <c r="K124" s="3" t="n">
-        <v>39036</v>
-      </c>
-      <c r="L124" s="3" t="n">
-        <v>45636</v>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>44883</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>a0R6g00000HgPZc</t>
+          <t>a0RKf00000JOaGo</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6563,36 +6581,34 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>17368_AQU001_2</t>
+          <t>19096_AQU001_2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>C#89526</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="n">
-        <v>45734</v>
+          <t>C#89525-32</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>45879</v>
       </c>
       <c r="I125" t="n">
         <v>1</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>RJP</t>
-        </is>
-      </c>
-      <c r="K125" s="3" t="n">
-        <v>39036</v>
-      </c>
-      <c r="L125" s="3" t="n">
-        <v>45636</v>
-      </c>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>a0R6g00000HgPZb</t>
+          <t>a0R3g00000BkpxC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6613,36 +6629,36 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>17368_AQU001_2</t>
+          <t>19096_AQU001_2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H126" s="3" t="n">
-        <v>45734</v>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>45088</v>
       </c>
       <c r="I126" t="n">
         <v>1</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>RJP</t>
-        </is>
-      </c>
-      <c r="K126" s="3" t="n">
-        <v>39036</v>
-      </c>
-      <c r="L126" s="3" t="n">
-        <v>45636</v>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>44887</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>a0R6g00000EUugN</t>
+          <t>a0R3g00000Bjcl9</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6663,34 +6679,36 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>18779_AQU001_2</t>
+          <t>19096_AQU001_2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>45088</v>
+      </c>
       <c r="I127" t="n">
         <v>1</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K127" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L127" s="3" t="n">
-        <v>45030</v>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>44883</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>a0RQQ00000HzOOb</t>
+          <t>a0R6g00000EUsi7</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6708,17 +6726,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>45756</v>
+      <c r="E128" s="3" t="n">
+        <v>45028</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>18779_AQU001_2</t>
+          <t>19096_AQU001_2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>C#89526</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -6727,20 +6745,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K128" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L128" s="3" t="n">
-        <v>46076</v>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>45028</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>a0R6g00000EUtiY</t>
+          <t>a0R0d0000068MOG</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6761,12 +6779,12 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>18779_AQU001_2</t>
+          <t>20088_AQU001_2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -6778,17 +6796,15 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K129" s="3" t="n">
+      <c r="K129" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L129" s="3" t="n">
-        <v>45030</v>
-      </c>
+      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>a0RKf00000JM5pl</t>
+          <t>a0R0d000005jYRw</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6809,16 +6825,16 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>18779_AQU001_2</t>
+          <t>20088_AQU001_2</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="n">
-        <v>45756</v>
+          <t>1517663</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>43538</v>
       </c>
       <c r="I130" t="n">
         <v>1</v>
@@ -6828,15 +6844,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K130" s="3" t="n">
+      <c r="K130" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L130" t="inlineStr"/>
+      <c r="L130" s="2" t="n">
+        <v>43024</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>a0R6g00000DLK3u</t>
+          <t>a0R0d000005jYRx</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6846,47 +6864,47 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>43024</v>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>19096_AQU001_2</t>
+          <t>20088_AQU001_2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H131" s="3" t="n">
-        <v>45088</v>
-      </c>
+          <t>1517663</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
         <v>1</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K131" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L131" s="3" t="n">
-        <v>44883</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>43024</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>a0R3g00000BkpxC</t>
+          <t>a0R6g00000HfNCo</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6907,36 +6925,34 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>19096_AQU001_2</t>
+          <t>20088_AQU001_2</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="n">
-        <v>45088</v>
+          <t>1567895</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>45489</v>
       </c>
       <c r="I132" t="n">
         <v>1</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K132" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L132" s="3" t="n">
-        <v>44887</v>
-      </c>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>a0R3g00000Bjcl9</t>
+          <t>a0R3g000009cMzU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6957,36 +6973,32 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>19096_AQU001_2</t>
+          <t>20991_AQU001_2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H133" s="3" t="n">
-        <v>45088</v>
-      </c>
+          <t>#AQUA</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
         <v>1</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K133" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L133" s="3" t="n">
-        <v>44883</v>
-      </c>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>41554</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>a0R6g00000EUsi7</t>
+          <t>a0R3g000008re25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6996,47 +7008,47 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="n">
-        <v>45088</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>19096_AQU001_2</t>
+          <t>20991_AQU001_2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>1543771</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>44651</v>
+      </c>
       <c r="I134" t="n">
         <v>1</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K134" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L134" s="3" t="n">
-        <v>45028</v>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>41554</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>44537</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>a0RKf00000JOaGo</t>
+          <t>a0R3g000008re24</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7057,34 +7069,36 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>19096_AQU001_2</t>
+          <t>20991_AQU001_2</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>C#89525-32</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="n">
-        <v>45879</v>
+          <t>1541637</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>44651</v>
       </c>
       <c r="I135" t="n">
         <v>1</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="K135" s="3" t="n">
-        <v>41486</v>
-      </c>
-      <c r="L135" t="inlineStr"/>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>41554</v>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>44537</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>a0R0d0000068MOG</t>
+          <t>a0R3g000008re3o</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7105,32 +7119,36 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>20088_AQU001_2</t>
+          <t>20991_AQU001_2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>44651</v>
+      </c>
       <c r="I136" t="n">
         <v>1</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K136" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L136" t="inlineStr"/>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>41554</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>44537</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>a0R0d000005jYRw</t>
+          <t>a0R3g000008re3p</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7151,36 +7169,36 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>20088_AQU001_2</t>
+          <t>20991_AQU001_2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>1517663</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="n">
-        <v>43538</v>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>44651</v>
       </c>
       <c r="I137" t="n">
         <v>1</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K137" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L137" s="3" t="n">
-        <v>43024</v>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>41554</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>44537</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>a0R0d000005jYRx</t>
+          <t>a0R3g000008re3q</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7190,47 +7208,47 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>43538</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>20088_AQU001_2</t>
+          <t>20991_AQU001_2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>1517663</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr"/>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>44651</v>
+      </c>
       <c r="I138" t="n">
         <v>1</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K138" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L138" s="3" t="n">
-        <v>43024</v>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>41554</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>44537</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>a0R6g00000HfNCo</t>
+          <t>a0R3g000008re3n</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7240,45 +7258,47 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>44537</v>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>20088_AQU001_2</t>
+          <t>20991_AQU001_2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H139" s="3" t="n">
-        <v>45489</v>
-      </c>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
         <v>1</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K139" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L139" t="inlineStr"/>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>41554</v>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>44537</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>a0R3g000008re3n</t>
+          <t>a0R6g00000F0tDs</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7296,17 +7316,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E140" s="2" t="n">
-        <v>44651</v>
+      <c r="E140" s="3" t="n">
+        <v>45105</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>20991_AQU001_2</t>
+          <t>30000111_AQU001_2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -7315,20 +7335,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K140" s="3" t="n">
-        <v>41554</v>
-      </c>
-      <c r="L140" s="3" t="n">
-        <v>44537</v>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>38517</v>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>45105</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>a0R3g000008re25</t>
+          <t>a0R6g00000F0ot5</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7349,36 +7369,36 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>20991_AQU001_2</t>
+          <t>30000111_AQU001_2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>1543771</t>
-        </is>
-      </c>
-      <c r="H141" s="3" t="n">
-        <v>44651</v>
+          <t>1554714</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>45827</v>
       </c>
       <c r="I141" t="n">
         <v>1</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K141" s="3" t="n">
-        <v>41554</v>
-      </c>
-      <c r="L141" s="3" t="n">
-        <v>44537</v>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>38517</v>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>45105</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>a0R3g000008re3o</t>
+          <t>a0R6g00000F0ot6</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7399,36 +7419,36 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>20991_AQU001_2</t>
+          <t>30000111_AQU001_2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H142" s="3" t="n">
-        <v>44651</v>
+          <t>1567024</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>45827</v>
       </c>
       <c r="I142" t="n">
         <v>1</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K142" s="3" t="n">
-        <v>41554</v>
-      </c>
-      <c r="L142" s="3" t="n">
-        <v>44537</v>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>38517</v>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>45105</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>a0R3g000008re3p</t>
+          <t>a0R3g000006jYj7</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7449,36 +7469,32 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>20991_AQU001_2</t>
+          <t>30000211_AQU001_2</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H143" s="3" t="n">
-        <v>44651</v>
-      </c>
+          <t>#AQUA</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
         <v>1</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K143" s="3" t="n">
-        <v>41554</v>
-      </c>
-      <c r="L143" s="3" t="n">
-        <v>44537</v>
-      </c>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>37010</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>a0R3g000008re3q</t>
+          <t>a0R3g0000067w89</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7499,36 +7515,36 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>20991_AQU001_2</t>
+          <t>30000211_AQU001_2</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="n">
-        <v>44651</v>
+          <t>1541637</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>44273</v>
       </c>
       <c r="I144" t="n">
         <v>1</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K144" s="3" t="n">
-        <v>41554</v>
-      </c>
-      <c r="L144" s="3" t="n">
-        <v>44537</v>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>37010</v>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>44160</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>a0R3g000009cMzU</t>
+          <t>a0R3g0000067w8B</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7538,23 +7554,25 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>44160</v>
+      </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>20991_AQU001_2</t>
+          <t>30000211_AQU001_2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>#AQUA</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -7563,18 +7581,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K145" s="3" t="n">
-        <v>41554</v>
-      </c>
-      <c r="L145" t="inlineStr"/>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>37010</v>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>44160</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>a0R3g000008re24</t>
+          <t>a0R3g0000067w8A</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7595,36 +7615,36 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>20991_AQU001_2</t>
+          <t>30000211_AQU001_2</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>1541637</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="n">
-        <v>44651</v>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>44273</v>
       </c>
       <c r="I146" t="n">
         <v>1</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K146" s="3" t="n">
-        <v>41554</v>
-      </c>
-      <c r="L146" s="3" t="n">
-        <v>44537</v>
+          <t>RNCA</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>37010</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>44160</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>a0R6g00000F0ot5</t>
+          <t>a0R6g00000HfZrp</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7634,47 +7654,47 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>45520</v>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>30000111_AQU001_2</t>
+          <t>30000578_AQU001_2</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>1554714</t>
-        </is>
-      </c>
-      <c r="H147" s="3" t="n">
-        <v>45827</v>
-      </c>
+          <t>#AQUA</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
         <v>1</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K147" s="3" t="n">
-        <v>38517</v>
-      </c>
-      <c r="L147" s="3" t="n">
-        <v>45105</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>45520</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>a0R6g00000F0tDs</t>
+          <t>a0R6g00000HfY81</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7692,17 +7712,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E148" s="2" t="n">
-        <v>45827</v>
+      <c r="E148" s="3" t="n">
+        <v>45520</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>30000111_AQU001_2</t>
+          <t>30000578_AQU001_2</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>#AQUA</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
@@ -7711,20 +7731,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K148" s="3" t="n">
-        <v>38517</v>
-      </c>
-      <c r="L148" s="3" t="n">
-        <v>45105</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>45520</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>a0R6g00000F0ot6</t>
+          <t>a0R6g00000HfY82</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7734,47 +7754,47 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>45520</v>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>30000111_AQU001_2</t>
+          <t>30000578_AQU001_2</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>1567024</t>
-        </is>
-      </c>
-      <c r="H149" s="3" t="n">
-        <v>45827</v>
-      </c>
+          <t>1554714</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
         <v>1</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K149" s="3" t="n">
-        <v>38517</v>
-      </c>
-      <c r="L149" s="3" t="n">
-        <v>45105</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>45520</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>a0R3g0000067w8A</t>
+          <t>a0RQQ00000IJCj3</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7795,36 +7815,32 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>30000211_AQU001_2</t>
+          <t>30000578_AQU001_2</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H150" s="3" t="n">
-        <v>44273</v>
-      </c>
-      <c r="I150" t="n">
-        <v>1</v>
-      </c>
+          <t>C#89525-32</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L150" s="3" t="n">
-        <v>44160</v>
-      </c>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>41089</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>a0R3g0000067w8B</t>
+          <t>a0R6g00000DLIYK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7834,25 +7850,23 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="n">
-        <v>44273</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>30000211_AQU001_2</t>
+          <t>30001009_AQU001_2</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -7861,20 +7875,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K151" s="3" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L151" s="3" t="n">
-        <v>44160</v>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>41520</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>a0R3g000006jYj7</t>
+          <t>a0R6g00000F09qv</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7895,12 +7909,12 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>30000211_AQU001_2</t>
+          <t>30001009_AQU001_2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>#AQUA</t>
+          <t>1541637</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -7909,18 +7923,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K152" s="3" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L152" t="inlineStr"/>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>41520</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>45050</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>a0R3g0000067w89</t>
+          <t>a0R3g000000aTtG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7930,73 +7946,75 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>44250</v>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>30000211_AQU001_2</t>
+          <t>30001009_AQU001_2</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>1541637</t>
-        </is>
-      </c>
-      <c r="H153" s="3" t="n">
-        <v>44273</v>
-      </c>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
         <v>1</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K153" s="3" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L153" s="3" t="n">
-        <v>44160</v>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>41520</v>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>a0R6g00000HfZrp</t>
+          <t>a0R3g000000aTtH</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
+          <t>Installed</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
           <t>Shipped</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>44250</v>
+      </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>30000578_AQU001_2</t>
+          <t>30001009_AQU001_2</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>#AQUA</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -8005,46 +8023,48 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K154" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L154" s="3" t="n">
-        <v>45520</v>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>41520</v>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>a0R6g00000HfY81</t>
+          <t>a0R3g000000aTtI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
+          <t>Installed</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
           <t>Shipped</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>44250</v>
+      </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>30000578_AQU001_2</t>
+          <t>30001009_AQU001_2</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -8053,30 +8073,30 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K155" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L155" s="3" t="n">
-        <v>45520</v>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>41520</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>a0R6g00000HfY82</t>
+          <t>a0R3g000000aTtC</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8087,12 +8107,12 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>30000578_AQU001_2</t>
+          <t>30001009_AQU001_2</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>1554714</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
@@ -8101,66 +8121,70 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K156" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L156" s="3" t="n">
-        <v>45520</v>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>41520</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>a0RQQ00000IJCj3</t>
+          <t>a0R3g000000aTtD</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
+          <t>Installed</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
           <t>Shipped</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
       <c r="D157" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" s="3" t="n">
+        <v>44250</v>
+      </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>30000578_AQU001_2</t>
+          <t>30001009_AQU001_2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>C#89525-32</t>
-        </is>
-      </c>
-      <c r="H157" s="3" t="n">
-        <v>46086</v>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="n">
+        <v>1</v>
+      </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K157" s="3" t="n">
-        <v>41089</v>
-      </c>
-      <c r="L157" t="inlineStr"/>
+          <t>RAP</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>41520</v>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>44250</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtC</t>
+          <t>a0R3g000000aTtE</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8170,15 +8194,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>44250</v>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
           <t>30001009_AQU001_2</t>
@@ -8198,17 +8224,17 @@
           <t>RAP</t>
         </is>
       </c>
-      <c r="K158" s="3" t="n">
+      <c r="K158" s="2" t="n">
         <v>41520</v>
       </c>
-      <c r="L158" s="3" t="n">
+      <c r="L158" s="2" t="n">
         <v>44250</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtD</t>
+          <t>a0R3g000000aTtF</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8226,7 +8252,9 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
+      <c r="E159" s="3" t="n">
+        <v>44250</v>
+      </c>
       <c r="F159" t="inlineStr">
         <is>
           <t>30001009_AQU001_2</t>
@@ -8246,17 +8274,17 @@
           <t>RAP</t>
         </is>
       </c>
-      <c r="K159" s="3" t="n">
+      <c r="K159" s="2" t="n">
         <v>41520</v>
       </c>
-      <c r="L159" s="3" t="n">
+      <c r="L159" s="2" t="n">
         <v>44250</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtE</t>
+          <t>a0R6g00000GtHbr</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8274,15 +8302,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" s="3" t="n">
+        <v>45147</v>
+      </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>30001009_AQU001_2</t>
+          <t>30001255_AQU001_2</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
@@ -8291,20 +8321,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K160" s="3" t="n">
-        <v>41520</v>
-      </c>
-      <c r="L160" s="3" t="n">
-        <v>44250</v>
+          <t>RTIMEA</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>41658</v>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>45147</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtF</t>
+          <t>a0R6g00000Gt15t</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -8314,45 +8344,47 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>30001009_AQU001_2</t>
+          <t>30001255_AQU001_2</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr"/>
+          <t>1554714</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>45720</v>
+      </c>
       <c r="I161" t="n">
         <v>1</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K161" s="3" t="n">
-        <v>41520</v>
-      </c>
-      <c r="L161" s="3" t="n">
-        <v>44250</v>
+          <t>RTIMEA</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>41658</v>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>45147</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtG</t>
+          <t>a0R6g00000Gt15u</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -8362,45 +8394,47 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>30001009_AQU001_2</t>
+          <t>30001255_AQU001_2</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr"/>
+          <t>1567024</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>45720</v>
+      </c>
       <c r="I162" t="n">
         <v>1</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K162" s="3" t="n">
-        <v>41520</v>
-      </c>
-      <c r="L162" s="3" t="n">
-        <v>44250</v>
+          <t>RTIMEA</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>41658</v>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>45147</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtH</t>
+          <t>a0R3g00000AEX6p</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -8410,23 +8444,23 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>30001009_AQU001_2</t>
+          <t>30005651_AQU001_2</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
@@ -8435,20 +8469,18 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K163" s="3" t="n">
-        <v>41520</v>
-      </c>
-      <c r="L163" s="3" t="n">
-        <v>44250</v>
-      </c>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>44057</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtI</t>
+          <t>a0R3g000009deUZ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8458,45 +8490,47 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>30001009_AQU001_2</t>
+          <t>30005651_AQU001_2</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr"/>
+          <t>1554713</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>44742</v>
+      </c>
       <c r="I164" t="n">
         <v>1</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K164" s="3" t="n">
-        <v>41520</v>
-      </c>
-      <c r="L164" s="3" t="n">
-        <v>44250</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>44057</v>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>44664</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>a0R6g00000DLIYK</t>
+          <t>a0RKf00000Kf14o</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8517,34 +8551,34 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>30001009_AQU001_2</t>
+          <t>30005651_AQU001_2</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr"/>
+          <t>1567895</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>45918</v>
+      </c>
       <c r="I165" t="n">
         <v>1</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K165" s="3" t="n">
-        <v>41520</v>
-      </c>
-      <c r="L165" s="3" t="n">
-        <v>44250</v>
-      </c>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>44057</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>a0R6g00000F09qv</t>
+          <t>a0R3g000009deUX</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -8565,34 +8599,36 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>30001009_AQU001_2</t>
+          <t>30005651_AQU001_2</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>1541637</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr"/>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>44742</v>
+      </c>
       <c r="I166" t="n">
         <v>1</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K166" s="3" t="n">
-        <v>41520</v>
-      </c>
-      <c r="L166" s="3" t="n">
-        <v>45050</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>44057</v>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>44664</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>a0R6g00000GtHbr</t>
+          <t>a0R3g000009deUY</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8610,17 +8646,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E167" s="2" t="n">
-        <v>45720</v>
+      <c r="E167" s="3" t="n">
+        <v>44664</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>30001255_AQU001_2</t>
+          <t>30005651_AQU001_2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>#AQUA</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
@@ -8629,20 +8665,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>RTIMEA</t>
-        </is>
-      </c>
-      <c r="K167" s="3" t="n">
-        <v>41658</v>
-      </c>
-      <c r="L167" s="3" t="n">
-        <v>45147</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>44057</v>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>44664</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>a0R6g00000Gt15t</t>
+          <t>a0R6g00000DLIUX</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8663,16 +8699,16 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>30001255_AQU001_2</t>
+          <t>30005885_AQU001_2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>1554714</t>
-        </is>
-      </c>
-      <c r="H168" s="3" t="n">
-        <v>45720</v>
+          <t>#AQUA</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>44582</v>
       </c>
       <c r="I168" t="n">
         <v>1</v>
@@ -8682,17 +8718,17 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K168" s="3" t="n">
-        <v>41658</v>
-      </c>
-      <c r="L168" s="3" t="n">
-        <v>45147</v>
+      <c r="K168" s="2" t="n">
+        <v>43950</v>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>44348</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>a0R6g00000Gt15u</t>
+          <t>a0R3g0000081SDb</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8713,16 +8749,16 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>30001255_AQU001_2</t>
+          <t>30005885_AQU001_2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>1567024</t>
-        </is>
-      </c>
-      <c r="H169" s="3" t="n">
-        <v>45720</v>
+          <t>1543770</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>44585</v>
       </c>
       <c r="I169" t="n">
         <v>1</v>
@@ -8732,17 +8768,17 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K169" s="3" t="n">
-        <v>41658</v>
-      </c>
-      <c r="L169" s="3" t="n">
-        <v>45147</v>
+      <c r="K169" s="2" t="n">
+        <v>43950</v>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>44348</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>a0R3g00000AEX6p</t>
+          <t>a0R3g0000081SDc</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8763,32 +8799,36 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>30005651_AQU001_2</t>
+          <t>30005885_AQU001_2</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr"/>
+          <t>1541637</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>44585</v>
+      </c>
       <c r="I170" t="n">
         <v>1</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K170" s="3" t="n">
-        <v>44057</v>
-      </c>
-      <c r="L170" t="inlineStr"/>
+          <t>RTIMEA</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>43950</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>44348</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>a0R3g000009deUZ</t>
+          <t>a0R6g00000HfncW</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8798,47 +8838,47 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>44585</v>
+      </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>30005651_AQU001_2</t>
+          <t>30005885_AQU001_2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>1554713</t>
-        </is>
-      </c>
-      <c r="H171" s="3" t="n">
-        <v>44742</v>
-      </c>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
         <v>1</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K171" s="3" t="n">
-        <v>44057</v>
-      </c>
-      <c r="L171" s="3" t="n">
-        <v>44664</v>
+          <t>RTIMEA</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>43950</v>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>45540</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>a0R3g000009deUX</t>
+          <t>a0R3g0000081SDd</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8859,36 +8899,36 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>30005651_AQU001_2</t>
+          <t>30005885_AQU001_2</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H172" s="3" t="n">
-        <v>44742</v>
+          <t>1541636</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>44585</v>
       </c>
       <c r="I172" t="n">
         <v>1</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K172" s="3" t="n">
-        <v>44057</v>
-      </c>
-      <c r="L172" s="3" t="n">
-        <v>44664</v>
+          <t>RTIMEA</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>43950</v>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>44348</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>a0R3g000009deUY</t>
+          <t>a0R6g00000DLIUN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8906,17 +8946,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E173" s="2" t="n">
-        <v>44742</v>
+      <c r="E173" s="3" t="n">
+        <v>44823</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>30005651_AQU001_2</t>
+          <t>30006224_AQU001_2</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
@@ -8928,17 +8968,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K173" s="3" t="n">
-        <v>44057</v>
-      </c>
-      <c r="L173" s="3" t="n">
-        <v>44664</v>
+      <c r="K173" s="2" t="n">
+        <v>43949</v>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>44823</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>a0RKf00000Kf14o</t>
+          <t>a0R3g00000AeY0L</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8959,16 +8999,16 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>30005651_AQU001_2</t>
+          <t>30006224_AQU001_2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H174" s="3" t="n">
-        <v>45918</v>
+          <t>1554711</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>46111</v>
       </c>
       <c r="I174" t="n">
         <v>1</v>
@@ -8978,15 +9018,17 @@
           <t>REU</t>
         </is>
       </c>
-      <c r="K174" s="3" t="n">
-        <v>44057</v>
-      </c>
-      <c r="L174" t="inlineStr"/>
+      <c r="K174" s="2" t="n">
+        <v>43949</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>44823</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>a0R6g00000DLIUX</t>
+          <t>a0R3g00000AeY0M</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -9007,36 +9049,36 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>30005885_AQU001_2</t>
+          <t>30006224_AQU001_2</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H175" s="3" t="n">
-        <v>44582</v>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>46111</v>
       </c>
       <c r="I175" t="n">
         <v>1</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>RTIMEA</t>
-        </is>
-      </c>
-      <c r="K175" s="3" t="n">
-        <v>43950</v>
-      </c>
-      <c r="L175" s="3" t="n">
-        <v>44348</v>
+          <t>REU</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>43949</v>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>44823</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>a0R6g00000HfncW</t>
+          <t>a0R6g00000DLITX</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -9054,17 +9096,17 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E176" s="2" t="n">
-        <v>44582</v>
+      <c r="E176" s="3" t="n">
+        <v>44886</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>30005885_AQU001_2</t>
+          <t>30006915_001_2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>#AQUA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -9076,17 +9118,17 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K176" s="3" t="n">
-        <v>43950</v>
-      </c>
-      <c r="L176" s="3" t="n">
-        <v>45540</v>
+      <c r="K176" s="2" t="n">
+        <v>43419</v>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>44886</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>a0R3g0000081SDb</t>
+          <t>a0R3g00000BkQwy</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -9107,17 +9149,15 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>30005885_AQU001_2</t>
+          <t>30006915_001_2</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>1543770</t>
-        </is>
-      </c>
-      <c r="H177" s="3" t="n">
-        <v>44585</v>
-      </c>
+          <t>1554711</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
         <v>1</v>
       </c>
@@ -9126,17 +9166,17 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K177" s="3" t="n">
-        <v>43950</v>
-      </c>
-      <c r="L177" s="3" t="n">
-        <v>44348</v>
+      <c r="K177" s="2" t="n">
+        <v>43419</v>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>44886</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>a0R3g0000081SDd</t>
+          <t>a0R3g00000BkQx0</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -9157,17 +9197,15 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>30005885_AQU001_2</t>
+          <t>30006915_001_2</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>1541636</t>
-        </is>
-      </c>
-      <c r="H178" s="3" t="n">
-        <v>44585</v>
-      </c>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>1</v>
       </c>
@@ -9176,17 +9214,17 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K178" s="3" t="n">
-        <v>43950</v>
-      </c>
-      <c r="L178" s="3" t="n">
-        <v>44348</v>
+      <c r="K178" s="2" t="n">
+        <v>43419</v>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>44886</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>a0R3g0000081SDc</t>
+          <t>a0R6g00000DLITS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -9196,28 +9234,28 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>44950</v>
+      </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>30005885_AQU001_2</t>
+          <t>30006926_001_2</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>1541637</t>
-        </is>
-      </c>
-      <c r="H179" s="3" t="n">
-        <v>44585</v>
-      </c>
+          <t>#AQUA</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>1</v>
       </c>
@@ -9226,17 +9264,17 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K179" s="3" t="n">
-        <v>43950</v>
-      </c>
-      <c r="L179" s="3" t="n">
-        <v>44348</v>
+      <c r="K179" s="2" t="n">
+        <v>44633</v>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>44950</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>a0R6g00000DLIUN</t>
+          <t>a0R6g00000DL8GR</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9246,47 +9284,47 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="n">
-        <v>46111</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>30006224_AQU001_2</t>
+          <t>30006926_001_2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr"/>
+          <t>1554713</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>45639</v>
+      </c>
       <c r="I180" t="n">
         <v>1</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K180" s="3" t="n">
-        <v>43949</v>
-      </c>
-      <c r="L180" s="3" t="n">
-        <v>44823</v>
+          <t>RTIMEA</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>44633</v>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>44950</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>a0R3g00000AeY0M</t>
+          <t>a0RKf00000JMoDX</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9307,36 +9345,34 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>30006224_AQU001_2</t>
+          <t>30006926_001_2</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H181" s="3" t="n">
-        <v>46111</v>
+          <t>1567895</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>45852</v>
       </c>
       <c r="I181" t="n">
         <v>1</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K181" s="3" t="n">
-        <v>43949</v>
-      </c>
-      <c r="L181" s="3" t="n">
-        <v>44823</v>
-      </c>
+          <t>RTIMEA</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>44633</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>a0R3g00000AeY0L</t>
+          <t>a0R6g00000DL8GQ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -9357,36 +9393,36 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>30006224_AQU001_2</t>
+          <t>30006926_001_2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>1554711</t>
-        </is>
-      </c>
-      <c r="H182" s="3" t="n">
-        <v>46111</v>
+          <t>1554712</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>45639</v>
       </c>
       <c r="I182" t="n">
         <v>1</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>REU</t>
-        </is>
-      </c>
-      <c r="K182" s="3" t="n">
-        <v>43949</v>
-      </c>
-      <c r="L182" s="3" t="n">
-        <v>44823</v>
+          <t>RTIMEA</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>44633</v>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>44950</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>a0R6g00000DLITX</t>
+          <t>a0R6g00000DLfkB</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -9404,10 +9440,12 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" s="3" t="n">
+        <v>45000</v>
+      </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>30006915_001_2</t>
+          <t>30007313_AQU001_2</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -9424,17 +9462,17 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K183" s="3" t="n">
-        <v>43419</v>
-      </c>
-      <c r="L183" s="3" t="n">
-        <v>44886</v>
+      <c r="K183" s="2" t="n">
+        <v>43551</v>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>a0R3g00000BkQx0</t>
+          <t>a0RKf00000JMurb</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -9455,15 +9493,17 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>30006915_001_2</t>
+          <t>30007313_AQU001_2</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr"/>
+          <t>1567895</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>45854</v>
+      </c>
       <c r="I184" t="n">
         <v>1</v>
       </c>
@@ -9472,17 +9512,15 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K184" s="3" t="n">
-        <v>43419</v>
-      </c>
-      <c r="L184" s="3" t="n">
-        <v>44886</v>
-      </c>
+      <c r="K184" s="2" t="n">
+        <v>43551</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>a0R3g00000BkQwy</t>
+          <t>a0R6g00000DLcdp</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9492,23 +9530,25 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>45000</v>
+      </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>30006915_001_2</t>
+          <t>30007313_AQU001_2</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>1554711</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
@@ -9520,354 +9560,12 @@
           <t>RTIMEA</t>
         </is>
       </c>
-      <c r="K185" s="3" t="n">
-        <v>43419</v>
-      </c>
-      <c r="L185" s="3" t="n">
-        <v>44886</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>a0R6g00000DLITS</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="n">
-        <v>45639</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>30006926_001_2</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="n">
-        <v>1</v>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>RTIMEA</t>
-        </is>
-      </c>
-      <c r="K186" s="3" t="n">
-        <v>44633</v>
-      </c>
-      <c r="L186" s="3" t="n">
-        <v>44950</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>a0R6g00000DL8GQ</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>30006926_001_2</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H187" s="3" t="n">
-        <v>45639</v>
-      </c>
-      <c r="I187" t="n">
-        <v>1</v>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>RTIMEA</t>
-        </is>
-      </c>
-      <c r="K187" s="3" t="n">
-        <v>44633</v>
-      </c>
-      <c r="L187" s="3" t="n">
-        <v>44950</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>a0R6g00000DL8GR</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>30006926_001_2</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>1554713</t>
-        </is>
-      </c>
-      <c r="H188" s="3" t="n">
-        <v>45639</v>
-      </c>
-      <c r="I188" t="n">
-        <v>1</v>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>RTIMEA</t>
-        </is>
-      </c>
-      <c r="K188" s="3" t="n">
-        <v>44633</v>
-      </c>
-      <c r="L188" s="3" t="n">
-        <v>44950</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>a0RKf00000JMoDX</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>30006926_001_2</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H189" s="3" t="n">
-        <v>45852</v>
-      </c>
-      <c r="I189" t="n">
-        <v>1</v>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>RTIMEA</t>
-        </is>
-      </c>
-      <c r="K189" s="3" t="n">
-        <v>44633</v>
-      </c>
-      <c r="L189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>a0R6g00000DLfkB</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>30007313_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="n">
-        <v>1</v>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>RTIMEA</t>
-        </is>
-      </c>
-      <c r="K190" s="3" t="n">
+      <c r="K185" s="2" t="n">
         <v>43551</v>
       </c>
-      <c r="L190" s="3" t="n">
+      <c r="L185" s="2" t="n">
         <v>45000</v>
       </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>a0R6g00000DLcdp</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>30007313_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="n">
-        <v>1</v>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>RTIMEA</t>
-        </is>
-      </c>
-      <c r="K191" s="3" t="n">
-        <v>43551</v>
-      </c>
-      <c r="L191" s="3" t="n">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>a0RKf00000JMurb</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>30007313_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H192" s="3" t="n">
-        <v>45854</v>
-      </c>
-      <c r="I192" t="n">
-        <v>1</v>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>RTIMEA</t>
-        </is>
-      </c>
-      <c r="K192" s="3" t="n">
-        <v>43551</v>
-      </c>
-      <c r="L192" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Mass_update_AQUA/mass_update_AQUA_sts_fix.xlsx
+++ b/Mass_update_AQUA/mass_update_AQUA_sts_fix.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a0R0d000006SiJ1</t>
+          <t>a0R3g000000Tj3U</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -606,15 +606,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>43619</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>10632_AQU001_2</t>
@@ -622,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1517662</t>
+          <t>1541637</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -638,13 +640,13 @@
         <v>37010</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43194</v>
+        <v>43851</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a0R3g000000Tj3U</t>
+          <t>a0R0d000006SiJ1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -654,17 +656,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>43619</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>10632_AQU001_2</t>
@@ -672,7 +672,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1541637</t>
+          <t>1517662</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -688,299 +688,7 @@
         <v>37010</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43851</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>a0R6g00000GtN5O</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>45166</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>30006827_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44623</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45166</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>a0RQQ00000LPak9</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>30006827_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>46191</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44623</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>a0R6g00000GtI48</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>45166</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>30006827_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44623</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45166</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>a0R6g00000HfzCu</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>45136</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>30007076_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>44854</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45560</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>a0RQQ00000LPax3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>30007076_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1567895</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>45136</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44854</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>a0R6g00000HfxY2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>45136</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>30007076_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1554712</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>RAP</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>44854</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>45560</v>
+        <v>43194</v>
       </c>
     </row>
   </sheetData>

--- a/Mass_update_AQUA/mass_update_AQUA_sts_fix.xlsx
+++ b/Mass_update_AQUA/mass_update_AQUA_sts_fix.xlsx
@@ -16,12 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -60,13 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,64 +436,29 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>right sts</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>sts equals parent?</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>sts equals parent?</t>
+          <t>Date Installed</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Date Installed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>Full Location Movex Id</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Product: Product Code</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Customer/Device Acceptance Date</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Account Region</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Date Shipped</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a0R3g000000U1rD</t>
+          <t>a0R3g000000Tj3U</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -510,185 +468,18 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>False</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+          <t>2019-06-03</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>10632_AQU001_2</t>
         </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>#AQUA</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43851</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>a0R3g000000Tj3T</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10632_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1543770</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>43851</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>a0R3g000000Tj3U</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>43619</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10632_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1541637</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>43851</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>a0R0d000006SiJ1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10632_AQU001_2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1517662</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>43194</v>
       </c>
     </row>
   </sheetData>
